--- a/dB/Script/Insert.xlsx
+++ b/dB/Script/Insert.xlsx
@@ -8,13 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Developer\Test-Mysql\dB\Script\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C4AC401-675E-4929-AA7A-B3443378E635}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C85CC42A-E3B8-4A09-A80C-EB47936D12B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{9845E99D-4D2D-477D-BDE6-AA77015FE430}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{9845E99D-4D2D-477D-BDE6-AA77015FE430}"/>
   </bookViews>
   <sheets>
     <sheet name="Usuarios" sheetId="1" r:id="rId1"/>
     <sheet name="Categorías " sheetId="2" r:id="rId2"/>
+    <sheet name="Estados " sheetId="3" r:id="rId3"/>
+    <sheet name="Tickets" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,10 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="16">
-  <si>
-    <t>')</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="32">
   <si>
     <t>Juan Pérez</t>
   </si>
@@ -75,6 +74,9 @@
     <t>INSERT INTO usuarios (nombre, email, area) values ('</t>
   </si>
   <si>
+    <t>',</t>
+  </si>
+  <si>
     <t>','</t>
   </si>
   <si>
@@ -88,6 +90,54 @@
   </si>
   <si>
     <t>INSERT INTO Categorias (nombre) values ('</t>
+  </si>
+  <si>
+    <t>Abierto</t>
+  </si>
+  <si>
+    <t>En Proceso</t>
+  </si>
+  <si>
+    <t>Cerrado</t>
+  </si>
+  <si>
+    <t>');</t>
+  </si>
+  <si>
+    <t>INSERT INTO Estados  (nombre) values ('</t>
+  </si>
+  <si>
+    <t>No hay internet en piso 3</t>
+  </si>
+  <si>
+    <t>Impresora no imprime</t>
+  </si>
+  <si>
+    <t>Error al abrir Excel</t>
+  </si>
+  <si>
+    <t>Correo no sincroniza</t>
+  </si>
+  <si>
+    <t>Los equipos no conectan a la red</t>
+  </si>
+  <si>
+    <t>La impresora del área no responde</t>
+  </si>
+  <si>
+    <t>Excel se cierra al abrir archivos</t>
+  </si>
+  <si>
+    <t>Outlook no actualiza correos</t>
+  </si>
+  <si>
+    <t>INSERT INTO tickets  (titulo,descripcion,usuario_id,categoria_id,estado_id) values ('</t>
+  </si>
+  <si>
+    <t>,</t>
+  </si>
+  <si>
+    <t>);</t>
   </si>
 </sst>
 </file>
@@ -510,83 +560,83 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>11</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>11</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I1" t="str">
         <f>_xlfn.CONCAT(A1,B1,C1,D1,E1,F1,G1)</f>
-        <v>INSERT INTO usuarios (nombre, email, area) values ('Juan Pérez','juan@mail.com','Sistemas')</v>
+        <v>INSERT INTO usuarios (nombre, email, area) values ('Juan Pérez','juan@mail.com','Sistemas');</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>11</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>11</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I2" t="str">
         <f t="shared" ref="I2:I3" si="0">_xlfn.CONCAT(A2,B2,C2,D2,E2,F2,G2)</f>
-        <v>INSERT INTO usuarios (nombre, email, area) values ('Ana Gómez','ana@mail.com','Contabilidad')</v>
+        <v>INSERT INTO usuarios (nombre, email, area) values ('Ana Gómez','ana@mail.com','Contabilidad');</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>11</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>11</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I3" t="str">
         <f t="shared" si="0"/>
-        <v>INSERT INTO usuarios (nombre, email, area) values ('Carlos Ruiz','carlos@mail.com','Recursos Humanos')</v>
+        <v>INSERT INTO usuarios (nombre, email, area) values ('Carlos Ruiz','carlos@mail.com','Recursos Humanos');</v>
       </c>
     </row>
   </sheetData>
@@ -618,11 +668,11 @@
         <v>12</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E1" t="str">
         <f>_xlfn.CONCAT(A1,B1,C1)</f>
-        <v>INSERT INTO Categorias (nombre) values ('Red')</v>
+        <v>INSERT INTO Categorias (nombre) values ('Red');</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -633,11 +683,11 @@
         <v>13</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E2" t="str">
         <f t="shared" ref="E2:E3" si="0">_xlfn.CONCAT(A2,B2,C2)</f>
-        <v>INSERT INTO Categorias (nombre) values ('Hardware')</v>
+        <v>INSERT INTO Categorias (nombre) values ('Hardware');</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -648,11 +698,260 @@
         <v>14</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E3" t="str">
         <f t="shared" si="0"/>
-        <v>INSERT INTO Categorias (nombre) values ('Software')</v>
+        <v>INSERT INTO Categorias (nombre) values ('Software');</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CA4B6C8-1C35-4068-BB76-82E0C5012B13}">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="37.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="2.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="50.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" t="str">
+        <f>_xlfn.CONCAT(A1,B1,C1)</f>
+        <v>INSERT INTO Estados  (nombre) values ('Abierto');</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" t="str">
+        <f t="shared" ref="E2:E3" si="0">_xlfn.CONCAT(A2,B2,C2)</f>
+        <v>INSERT INTO Estados  (nombre) values ('En Proceso');</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO Estados  (nombre) values ('Cerrado');</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3F16925-674D-4B29-81E4-ABA553363EEA}">
+  <dimension ref="A1:K10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="76.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="2.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="32.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="2" customWidth="1"/>
+    <col min="8" max="8" width="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="2" customWidth="1"/>
+    <col min="10" max="10" width="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="2.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1" s="1">
+        <v>1</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="1">
+        <v>2</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H2" s="1">
+        <v>2</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2" s="1">
+        <v>2</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="1">
+        <v>3</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3" s="1">
+        <v>3</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3" s="1">
+        <v>3</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="1">
+        <v>1</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H4" s="1">
+        <v>3</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4" s="1">
+        <v>1</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" t="str">
+        <f>_xlfn.CONCAT(A1,B1,C1,D1,E1,F1,G1,H1,I1,J1,K1)</f>
+        <v>INSERT INTO tickets  (titulo,descripcion,usuario_id,categoria_id,estado_id) values ('No hay internet en piso 3','Los equipos no conectan a la red',1,1,1);</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" t="str">
+        <f t="shared" ref="A8:A10" si="0">_xlfn.CONCAT(A2,B2,C2,D2,E2,F2,G2,H2,I2,J2,K2)</f>
+        <v>INSERT INTO tickets  (titulo,descripcion,usuario_id,categoria_id,estado_id) values ('Impresora no imprime','La impresora del área no responde',2,2,2);</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO tickets  (titulo,descripcion,usuario_id,categoria_id,estado_id) values ('Error al abrir Excel','Excel se cierra al abrir archivos',3,3,3);</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO tickets  (titulo,descripcion,usuario_id,categoria_id,estado_id) values ('Correo no sincroniza','Outlook no actualiza correos',1,3,1);</v>
       </c>
     </row>
   </sheetData>

--- a/dB/Script/Insert.xlsx
+++ b/dB/Script/Insert.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Developer\Test-Mysql\dB\Script\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C85CC42A-E3B8-4A09-A80C-EB47936D12B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3476C5C-979C-425F-9D21-7151A64C7483}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{9845E99D-4D2D-477D-BDE6-AA77015FE430}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="4" xr2:uid="{9845E99D-4D2D-477D-BDE6-AA77015FE430}"/>
   </bookViews>
   <sheets>
     <sheet name="Usuarios" sheetId="1" r:id="rId1"/>
     <sheet name="Categorías " sheetId="2" r:id="rId2"/>
     <sheet name="Estados " sheetId="3" r:id="rId3"/>
     <sheet name="Tickets" sheetId="4" r:id="rId4"/>
+    <sheet name="Comentarios" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="38">
   <si>
     <t>Juan Pérez</t>
   </si>
@@ -138,6 +139,24 @@
   </si>
   <si>
     <t>);</t>
+  </si>
+  <si>
+    <t>INSERT INTO comentarios (ticket_id,usuario_id,texto) values (</t>
+  </si>
+  <si>
+    <t>,'</t>
+  </si>
+  <si>
+    <t>Revisé el cableado y está conectado</t>
+  </si>
+  <si>
+    <t>Sigue sin funcionar en mi equipo</t>
+  </si>
+  <si>
+    <t>Se reinició la impresora y ya imprime</t>
+  </si>
+  <si>
+    <t>Se reinstaló Office y quedó solucionado</t>
   </si>
 </sst>
 </file>
@@ -203,7 +222,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -211,6 +230,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -958,4 +980,133 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{542B85D8-D60D-45A8-96A9-D4DEFF371F81}">
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="56.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="1.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="2" customWidth="1"/>
+    <col min="6" max="6" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="2.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="97.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="1">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="I1" s="1" t="str">
+        <f>_xlfn.CONCAT(A1,B1,C1,D1,E1,F1,G1)</f>
+        <v>INSERT INTO comentarios (ticket_id,usuario_id,texto) values (1,1,'Revisé el cableado y está conectado');</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" s="1">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="1">
+        <v>2</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="1" t="str">
+        <f t="shared" ref="I2:I4" si="0">_xlfn.CONCAT(A2,B2,C2,D2,E2,F2,G2)</f>
+        <v>INSERT INTO comentarios (ticket_id,usuario_id,texto) values (1,2,'Sigue sin funcionar en mi equipo');</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="1">
+        <v>2</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" s="1">
+        <v>3</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO comentarios (ticket_id,usuario_id,texto) values (2,3,'Se reinició la impresora y ya imprime');</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="1">
+        <v>3</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" s="1">
+        <v>1</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="I4" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO comentarios (ticket_id,usuario_id,texto) values (3,1,'Se reinstaló Office y quedó solucionado');</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>